--- a/WAHPConfigFile.xlsx
+++ b/WAHPConfigFile.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RollLe01\OneDrive - Reed Elsevier Group ICO Reed Elsevier Inc\Documents\UiPath\WAHPMatchingAutomation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02763DFC-065A-4FD3-9796-470E4A21E040}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7821194A-E6F0-4F2D-B05C-C2F9B10677B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{42A39E5C-086F-4F21-8E01-13B402E1EF9B}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="53">
   <si>
     <t>Name</t>
   </si>
@@ -193,6 +193,9 @@
   </si>
   <si>
     <t>WAHP SP to Virtual Desktop - Testing</t>
+  </si>
+  <si>
+    <t>agnes.sara@lexisnexisrisk.com; gerard.mancenido@lexisnexisrisk.com; lester.rollan@lexisnexisrisk.com; dindee.galindo@lexisnexisrisk.com; jesriel.tolentino@lexisnexisrisk.com; paul.fabro@lexisnexisrisk.com; judy.cotaoco@lexisnexisrisk.com</t>
   </si>
 </sst>
 </file>
@@ -744,7 +747,7 @@
         <v>29</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>31</v>
